--- a/demo-StatsPAI-skill/tables/table2d_multi_outcome.xlsx
+++ b/demo-StatsPAI-skill/tables/table2d_multi_outcome.xlsx
@@ -53,7 +53,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -62,7 +62,30 @@
       <diagonal/>
     </border>
     <border>
-      <bottom style="medium"/>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -70,17 +93,23 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -449,12 +478,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,99 +493,551 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>(2)</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>4.621***</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>-426.712***</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>(0.074)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>(49.448)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Years of schooling</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>0.075***</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>45.411***</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>(0.004)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>(2.464)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>exper</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>0.085***</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>51.754***</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>(0.007)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>(3.895)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>expersq</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>-1.372***</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>(0.173)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>-0.199***</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>-99.882***</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>(0.018)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>(9.291)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>south</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>-0.148***</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>-72.429***</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>(0.028)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>(16.495)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>smsa</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>0.136***</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>71.931***</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>(0.019)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>(10.967)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>smsa66</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>0.026</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>18.150</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>(0.019)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>(11.329)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>reg662</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>0.096***</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>65.585***</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>(0.035)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>(21.057)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>reg663</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>0.145***</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>82.568***</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>(0.034)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>(19.941)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>reg664</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>0.055</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>25.589</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>(0.041)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>(23.632)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>reg665</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>0.128***</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>70.469***</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>(0.043)</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>(24.789)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>reg666</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>0.141***</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>77.607***</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>(0.045)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>(25.420)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>reg667</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>0.118***</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>65.984**</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>(0.046)</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>(26.284)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>reg668</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>-0.056</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-40.196</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>(0.051)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>(28.333)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>reg669</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>0.119***</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>81.790***</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>(0.039)</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>(24.109)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>3,010</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>3,010</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>R²</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>0.300</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>0.281</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Standard errors in parentheses</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>* p&lt;0.10, ** p&lt;0.05, *** p&lt;0.01</t>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>*** p&lt;0.01, ** p&lt;0.05, * p&lt;0.10</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>